--- a/contenus/tab2/exs2-recherchev-fiche-produit.xlsx
+++ b/contenus/tab2/exs2-recherchev-fiche-produit.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consignes" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercice" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correction" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1073,476 +1072,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Référence</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Désignation</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Catégorie</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Fournisseur</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>REF109</t>
-        </is>
-      </c>
-      <c r="B2">
-        <f>VLOOKUP(A2,$F$2:$J$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="C2">
-        <f>VLOOKUP(A2,$F$2:$J$13,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="D2">
-        <f>VLOOKUP(A2,$F$2:$J$13,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>REF101</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Palette Europe</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Bois</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>FournisseurPalettes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>REF103</t>
-        </is>
-      </c>
-      <c r="B3">
-        <f>VLOOKUP(A3,$F$2:$J$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="C3">
-        <f>VLOOKUP(A3,$F$2:$J$13,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="D3">
-        <f>VLOOKUP(A3,$F$2:$J$13,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>REF102</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Carton simple cannelure</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Emballage</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>CartonPlus</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>REF107</t>
-        </is>
-      </c>
-      <c r="B4">
-        <f>VLOOKUP(A4,$F$2:$J$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="C4">
-        <f>VLOOKUP(A4,$F$2:$J$13,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="D4">
-        <f>VLOOKUP(A4,$F$2:$J$13,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>REF103</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Film étirable</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Emballage</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>EmballagePro</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>REF102</t>
-        </is>
-      </c>
-      <c r="B5">
-        <f>VLOOKUP(A5,$F$2:$J$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="C5">
-        <f>VLOOKUP(A5,$F$2:$J$13,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="D5">
-        <f>VLOOKUP(A5,$F$2:$J$13,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>REF104</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Casque de chantier</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>EPI</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>SecuEquip</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>REF111</t>
-        </is>
-      </c>
-      <c r="B6">
-        <f>VLOOKUP(A6,$F$2:$J$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="C6">
-        <f>VLOOKUP(A6,$F$2:$J$13,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="D6">
-        <f>VLOOKUP(A6,$F$2:$J$13,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>REF105</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Gants de manutention</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>EPI</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>SecuEquip</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>REF105</t>
-        </is>
-      </c>
-      <c r="B7">
-        <f>VLOOKUP(A7,$F$2:$J$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="C7">
-        <f>VLOOKUP(A7,$F$2:$J$13,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="D7">
-        <f>VLOOKUP(A7,$F$2:$J$13,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>REF106</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Transpalette manuel</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Matériel</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>350</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>LogiMat</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>REF110</t>
-        </is>
-      </c>
-      <c r="B8">
-        <f>VLOOKUP(A8,$F$2:$J$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="C8">
-        <f>VLOOKUP(A8,$F$2:$J$13,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="D8">
-        <f>VLOOKUP(A8,$F$2:$J$13,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>REF107</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Chariot élévateur électrique</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Matériel</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>18500</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>LogiMat</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>REF112</t>
-        </is>
-      </c>
-      <c r="B9">
-        <f>VLOOKUP(A9,$F$2:$J$13,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="C9">
-        <f>VLOOKUP(A9,$F$2:$J$13,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="D9">
-        <f>VLOOKUP(A9,$F$2:$J$13,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>REF108</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Étiquette code-barres</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Emballage</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>EmballagePro</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>REF109</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Chaussures de sécurité</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>EPI</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>45</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>SecuEquip</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>REF110</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Sangle d'arrimage</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>LogiMat</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>REF111</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Cadenas de sécurité</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Accessoire</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>SecuEquip</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>REF112</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Extincteur portatif</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sécurité</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>65</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>SecuEquip</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>